--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484595_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484595_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.684799999999999</v>
+        <v>9.0938</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1584</v>
+        <v>5.7904</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5264</v>
+        <v>3.3035</v>
       </c>
       <c r="G2" t="n">
         <v>3.1005</v>
@@ -610,13 +610,13 @@
         <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9954</v>
+        <v>2.4044</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8771</v>
+        <v>1.5091</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1183</v>
+        <v>0.8953</v>
       </c>
       <c r="V2" t="n">
         <v>2.8559</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.01</v>
+        <v>1.9076</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6874</v>
+        <v>2.0309</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3226</v>
+        <v>-0.1233</v>
       </c>
       <c r="G3" t="n">
         <v>4.0676</v>
@@ -688,13 +688,13 @@
         <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2985</v>
+        <v>1.1961</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2911</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0074</v>
+        <v>0.5614</v>
       </c>
       <c r="V3" t="n">
         <v>-1.89</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2753</v>
+        <v>1.3224</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2753</v>
+        <v>0.0336</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.2888</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2753</v>
+        <v>-1.1675</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6502</v>
+        <v>-0.9302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6251</v>
+        <v>-0.2373</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2753</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6502</v>
+        <v>-0.1333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6251</v>
+        <v>-0.5577</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.4765</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.7968</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.3204</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.0134</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.0673</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8248</v>
+        <v>1.2753</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7775</v>
+        <v>1.2753</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6023</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0531</v>
+        <v>1.2753</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9535</v>
+        <v>0.6502</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09959999999999999</v>
+        <v>0.6251</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9035</v>
+        <v>1.2753</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0285</v>
+        <v>0.6502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.125</v>
+        <v>0.6251</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1496</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.925</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2246</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1991</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5951</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0423</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5528</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6565</v>
+        <v>0.9231</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4103</v>
+        <v>-0.2179</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0667</v>
+        <v>1.1411</v>
       </c>
       <c r="G6" t="n">
         <v>0.2404</v>
@@ -922,13 +922,13 @@
         <v>0.3665</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0495</v>
+        <v>0.3162</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2753</v>
+        <v>-0.083</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3248</v>
+        <v>0.3991</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4352</v>
+        <v>0.4154</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-1.1621</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3631</v>
+        <v>1.5775</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1675</v>
+        <v>-2.0531</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9302</v>
+        <v>-1.9535</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2373</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.9035</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1333</v>
+        <v>-1.0285</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5577</v>
+        <v>0.125</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4765</v>
+        <v>-1.1496</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7968</v>
+        <v>-0.925</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3204</v>
+        <v>-0.2246</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8738</v>
+        <v>1.1857</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8808</v>
+        <v>0.6576</v>
       </c>
       <c r="U7" t="n">
-        <v>0.007</v>
+        <v>0.5281</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>V. PRADA SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4558</v>
+        <v>0.0192</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8883</v>
+        <v>0.6857</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4325</v>
+        <v>-0.6665</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7585</v>
+        <v>-0.4559</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.832</v>
+        <v>-1.3438</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0735</v>
+        <v>0.8879</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.757</v>
+        <v>1.9853</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6321</v>
+        <v>-0.666</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8752</v>
+        <v>2.6512</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0015</v>
+        <v>-2.4412</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1999</v>
+        <v>-0.6778</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8017</v>
+        <v>-1.7633</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8366</v>
+        <v>0.4255</v>
       </c>
       <c r="T8" t="n">
-        <v>1.408</v>
+        <v>0.4834</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4286</v>
+        <v>-0.0579</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6335</v>
+        <v>0.9658</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6231</v>
+        <v>0.9658</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. PRADA SANCHEZ</t>
+          <t>H. RUEDA RIOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4566</v>
+        <v>-0.5795</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3833</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8399</v>
+        <v>-1.5417</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4559</v>
+        <v>1.3356</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3438</v>
+        <v>-1.8478</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8879</v>
+        <v>3.1835</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9853</v>
+        <v>3.4637</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.666</v>
+        <v>-0.4893</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6512</v>
+        <v>3.953</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4412</v>
+        <v>-2.1281</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6778</v>
+        <v>-1.3585</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7633</v>
+        <v>-0.7695</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9163</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7489</v>
+        <v>-3.6651</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0503</v>
+        <v>1.017</v>
       </c>
       <c r="T9" t="n">
-        <v>0.181</v>
+        <v>0.5302</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2313</v>
+        <v>0.4868</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9658</v>
+        <v>0.6335</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6531</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2329</v>
+        <v>-1.259</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8413</v>
+        <v>0.6059</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1213</v>
+        <v>-2.7585</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9357</v>
+        <v>-2.832</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8144</v>
+        <v>0.0735</v>
       </c>
       <c r="J10" t="n">
-        <v>1.303</v>
+        <v>-0.757</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2197</v>
+        <v>-1.6321</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0833</v>
+        <v>0.8752</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1818</v>
+        <v>-2.0015</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.284</v>
+        <v>-1.1999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.8017</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4798</v>
+        <v>1.6393</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4563</v>
+        <v>1.0374</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0235</v>
+        <v>0.602</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6231</v>
+        <v>-0.6335</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2224</v>
+        <v>-0.6231</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5993</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. RUEDA RIOS</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0247</v>
+        <v>-0.8914</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4675</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4922</v>
+        <v>-1.8908</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3356</v>
+        <v>0.1213</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8478</v>
+        <v>0.9357</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1835</v>
+        <v>-0.8144</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4637</v>
+        <v>1.303</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4893</v>
+        <v>1.2197</v>
       </c>
       <c r="L11" t="n">
-        <v>3.953</v>
+        <v>0.0833</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1281</v>
+        <v>-1.1818</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3585</v>
+        <v>-0.284</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7695</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9321</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R11" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5718</v>
+        <v>0.1968</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0355</v>
+        <v>0.2229</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5363</v>
+        <v>-0.026</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6335</v>
+        <v>2.2224</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6335</v>
+        <v>-1.5993</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2421</v>
+        <v>-1.9837</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2456</v>
+        <v>-0.6198</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4877</v>
+        <v>-1.3639</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5775</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1625</v>
+        <v>0.421</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5928</v>
+        <v>0.7274</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4302</v>
+        <v>-0.3064</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2774</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4317</v>
+        <v>-5.6315</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1112</v>
+        <v>-4.6331</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3205</v>
+        <v>-0.9984</v>
       </c>
       <c r="G13" t="n">
         <v>-5.9745</v>
@@ -1468,13 +1468,13 @@
         <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9093</v>
+        <v>0.7095</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2074</v>
+        <v>0.6855</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2981</v>
+        <v>0.0239</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.667299999999998</v>
+        <v>5.217599999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3352</v>
+        <v>3.885699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.332</v>
+        <v>1.3322</v>
       </c>
       <c r="G14" t="n">
         <v>-2.846300000000002</v>
@@ -1525,7 +1525,7 @@
         <v>2.244999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>7.054200000000001</v>
+        <v>7.054199999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-12.1457</v>
@@ -1537,7 +1537,7 @@
         <v>-3.047499999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.749</v>
+        <v>-2.749000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-19.2421</v>
@@ -1546,16 +1546,16 @@
         <v>16.4932</v>
       </c>
       <c r="S14" t="n">
-        <v>8.974399999999999</v>
+        <v>9.524899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>5.9354</v>
+        <v>6.485800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0391</v>
+        <v>3.039</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2878</v>
+        <v>1.287800000000001</v>
       </c>
       <c r="W14" t="n">
         <v>7.3423</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6038</v>
+        <v>7.5731</v>
       </c>
       <c r="E15" t="n">
-        <v>6.145</v>
+        <v>6.3373</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4588</v>
+        <v>1.2358</v>
       </c>
       <c r="G15" t="n">
         <v>4.7064</v>
@@ -1624,13 +1624,13 @@
         <v>2.7489</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5137</v>
+        <v>-0.5443</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.46</v>
+        <v>-0.2677</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0537</v>
+        <v>-0.2766</v>
       </c>
       <c r="V15" t="n">
         <v>1.5785</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2857</v>
+        <v>2.802</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7666</v>
+        <v>2.382</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5191</v>
+        <v>0.42</v>
       </c>
       <c r="G16" t="n">
         <v>2.1127</v>
@@ -1702,13 +1702,13 @@
         <v>2.7489</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3768</v>
+        <v>-0.8605</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3092</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.7851</v>
       </c>
       <c r="V16" t="n">
         <v>0.6335</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2612</v>
+        <v>1.3355</v>
       </c>
       <c r="E17" t="n">
         <v>1.3002</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.039</v>
+        <v>0.0353</v>
       </c>
       <c r="G17" t="n">
         <v>1.5231</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2619</v>
+        <v>-0.1876</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2069</v>
+        <v>-0.1325</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7675</v>
+        <v>0.3304</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1005</v>
+        <v>-0.188</v>
       </c>
       <c r="F18" t="n">
-        <v>0.667</v>
+        <v>0.5184</v>
       </c>
       <c r="G18" t="n">
         <v>1.6537</v>
@@ -1858,13 +1858,13 @@
         <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1715</v>
+        <v>-0.6086</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0536</v>
+        <v>-0.2349</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2251</v>
+        <v>-0.3737</v>
       </c>
       <c r="V18" t="n">
         <v>0.9346</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0581</v>
+        <v>0.1643</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.503</v>
       </c>
       <c r="F19" t="n">
-        <v>0.132</v>
+        <v>-0.3387</v>
       </c>
       <c r="G19" t="n">
         <v>0.8253</v>
@@ -1936,13 +1936,13 @@
         <v>2.7489</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0996</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.101</v>
+        <v>-0.5241</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0014</v>
+        <v>-0.4693</v>
       </c>
       <c r="V19" t="n">
         <v>0.3324</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6081</v>
+        <v>-0.525</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2141</v>
+        <v>-1.5025</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6059</v>
+        <v>0.9775</v>
       </c>
       <c r="G20" t="n">
         <v>0.519</v>
@@ -2014,13 +2014,13 @@
         <v>2.3823</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2817</v>
+        <v>-2.1985</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.405</v>
+        <v>-0.6934</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8767</v>
+        <v>-1.5051</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3115</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6801</v>
+        <v>-1.5097</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5638</v>
+        <v>-0.4676</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1164</v>
+        <v>-1.0421</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7924</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2438</v>
+        <v>-0.0733</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0369</v>
+        <v>0.0592</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2069</v>
+        <v>-0.1325</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6439</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4642</v>
+        <v>-1.9805</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0805</v>
+        <v>0.3041</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3837</v>
+        <v>-2.2846</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9617</v>
@@ -2170,13 +2170,13 @@
         <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3193</v>
+        <v>0.1644</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2572</v>
+        <v>0.1275</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0621</v>
+        <v>0.0369</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6335</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5822</v>
+        <v>-2.5356</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0083</v>
+        <v>-0.9121</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5739</v>
+        <v>-1.6235</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9709</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2344</v>
+        <v>-0.1878</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.092</v>
+        <v>0.0042</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1424</v>
+        <v>-0.1919</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6439</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0949</v>
+        <v>-3.8146</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4877</v>
+        <v>-5.2569</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3928</v>
+        <v>1.4423</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7539</v>
@@ -2326,13 +2326,13 @@
         <v>3.8484</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7913</v>
+        <v>-1.5109</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3816</v>
+        <v>-0.3876</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1729</v>
+        <v>-1.1233</v>
       </c>
       <c r="V24" t="n">
         <v>1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2138</v>
+        <v>-6.5071</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2161</v>
+        <v>-3.8314</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9977</v>
+        <v>-2.6757</v>
       </c>
       <c r="G25" t="n">
         <v>-2.0152</v>
@@ -2404,13 +2404,13 @@
         <v>3.1154</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.6805</v>
+        <v>-1.9738</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3763</v>
+        <v>-0.9917</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3042</v>
+        <v>-0.9821</v>
       </c>
       <c r="V25" t="n">
         <v>-3.8009</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.667</v>
+        <v>-4.667199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.3321</v>
+        <v>-1.3319</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.3351</v>
+        <v>-3.3353</v>
       </c>
       <c r="G26" t="n">
         <v>2.8461</v>
@@ -2482,13 +2482,13 @@
         <v>19.2421</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.974499999999999</v>
+        <v>-8.974300000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.0391</v>
+        <v>-3.039</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.935499999999999</v>
+        <v>-5.9352</v>
       </c>
       <c r="V26" t="n">
         <v>-1.287700000000001</v>
